--- a/herramientas/plantilla-factura-excel/plantilla-registro-gastos-ingresos.xlsx
+++ b/herramientas/plantilla-factura-excel/plantilla-registro-gastos-ingresos.xlsx
@@ -18,10 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
-  </numFmts>
-  <fonts count="18">
+  <numFmts count="0"/>
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,35 +43,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FF1A1814"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FFD45A2A"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="FF4A4740"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -85,14 +54,8 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FF2AB87A"/>
+      <color rgb="FFD45A2A"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FF2AB87A"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -102,14 +65,49 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="FF1A1814"/>
-      <sz val="10"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF1A1814"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1A1814"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF2AB87A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFD45A2A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF2AB87A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="FF4A4740"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -121,16 +119,27 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="FFD45A2A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF1A1814"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="FF1A1814"/>
-      <sz val="14"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -164,16 +173,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCC4444"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -195,11 +199,44 @@
         <color rgb="FFDDD8CE"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFDDD8CE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDDD8CE"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDD8CE"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDDD8CE"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDD8CE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDDD8CE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -208,85 +245,122 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -656,13 +730,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -676,18 +750,18 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AutónomoLab — autonomolab.com | Las celdas en naranja son editables</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>AutonomoLab — autonomolab.com  |  Celdas naranjas = editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>CONFIGURACIÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>CONFIGURACION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Año:</t>
@@ -696,8 +770,9 @@
       <c r="B5" s="5" t="n">
         <v>2026</v>
       </c>
-    </row>
-    <row r="6">
+      <c r="C5" s="6" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Mes:</t>
@@ -708,859 +783,867 @@
           <t>Mayo</t>
         </is>
       </c>
-    </row>
-    <row r="7">
+      <c r="C6" s="6" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Nombre/Negocio:</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Tu nombre aquí</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>📥  INGRESOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+          <t>Nombre:</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Tu nombre aqui</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n"/>
+    </row>
+    <row r="8" ht="10" customHeight="1"/>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  INGRESOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Nº Factura</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>N° Factura</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Cliente</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Base €</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>IVA €</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>Total €</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>IRPF ret.</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>Cobrado €</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="n"/>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="11">
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Cobrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="12" t="n"/>
+      <c r="G11" s="13">
         <f>IF(E11="","",E11+F11)</f>
         <v/>
       </c>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="13">
+      <c r="H11" s="14" t="n"/>
+      <c r="I11" s="15">
         <f>IF(G11="","",G11-H11)</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="n"/>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="11">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="13">
         <f>IF(E12="","",E12+F12)</f>
         <v/>
       </c>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="13">
+      <c r="H12" s="14" t="n"/>
+      <c r="I12" s="15">
         <f>IF(G12="","",G12-H12)</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="9" t="n"/>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="11">
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="13">
         <f>IF(E13="","",E13+F13)</f>
         <v/>
       </c>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="13">
+      <c r="H13" s="14" t="n"/>
+      <c r="I13" s="15">
         <f>IF(G13="","",G13-H13)</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="11">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="13">
         <f>IF(E14="","",E14+F14)</f>
         <v/>
       </c>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="13">
+      <c r="H14" s="14" t="n"/>
+      <c r="I14" s="15">
         <f>IF(G14="","",G14-H14)</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="9" t="n"/>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="11">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="13">
         <f>IF(E15="","",E15+F15)</f>
         <v/>
       </c>
-      <c r="H15" s="12" t="n"/>
-      <c r="I15" s="13">
+      <c r="H15" s="14" t="n"/>
+      <c r="I15" s="15">
         <f>IF(G15="","",G15-H15)</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="9" t="n"/>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="11">
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="13">
         <f>IF(E16="","",E16+F16)</f>
         <v/>
       </c>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="13">
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="15">
         <f>IF(G16="","",G16-H16)</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="11">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="13">
         <f>IF(E17="","",E17+F17)</f>
         <v/>
       </c>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="13">
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="15">
         <f>IF(G17="","",G17-H17)</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="9" t="n"/>
-      <c r="G18" s="11">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="13">
         <f>IF(E18="","",E18+F18)</f>
         <v/>
       </c>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="13">
+      <c r="H18" s="14" t="n"/>
+      <c r="I18" s="15">
         <f>IF(G18="","",G18-H18)</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="11">
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="13">
         <f>IF(E19="","",E19+F19)</f>
         <v/>
       </c>
-      <c r="H19" s="12" t="n"/>
-      <c r="I19" s="13">
+      <c r="H19" s="14" t="n"/>
+      <c r="I19" s="15">
         <f>IF(G19="","",G19-H19)</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="11">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="13">
         <f>IF(E20="","",E20+F20)</f>
         <v/>
       </c>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="13">
+      <c r="H20" s="14" t="n"/>
+      <c r="I20" s="15">
         <f>IF(G20="","",G20-H20)</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="9" t="n"/>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="11">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="13">
         <f>IF(E21="","",E21+F21)</f>
         <v/>
       </c>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="13">
+      <c r="H21" s="14" t="n"/>
+      <c r="I21" s="15">
         <f>IF(G21="","",G21-H21)</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="11">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="13">
         <f>IF(E22="","",E22+F22)</f>
         <v/>
       </c>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="13">
+      <c r="H22" s="14" t="n"/>
+      <c r="I22" s="15">
         <f>IF(G22="","",G22-H22)</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="9" t="n"/>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="10" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="11">
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="13">
         <f>IF(E23="","",E23+F23)</f>
         <v/>
       </c>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="13">
+      <c r="H23" s="14" t="n"/>
+      <c r="I23" s="15">
         <f>IF(G23="","",G23-H23)</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="9" t="n"/>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="11">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="13">
         <f>IF(E24="","",E24+F24)</f>
         <v/>
       </c>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="13">
+      <c r="H24" s="14" t="n"/>
+      <c r="I24" s="15">
         <f>IF(G24="","",G24-H24)</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="9" t="n"/>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="11">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="13">
         <f>IF(E25="","",E25+F25)</f>
         <v/>
       </c>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="13">
+      <c r="H25" s="14" t="n"/>
+      <c r="I25" s="15">
         <f>IF(G25="","",G25-H25)</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>TOTAL INGRESOS</t>
-        </is>
-      </c>
-      <c r="E26" s="15">
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOTAL INGRESOS</t>
+        </is>
+      </c>
+      <c r="E26" s="17">
         <f>SUM(E11:E25)</f>
         <v/>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="17">
         <f>SUM(F11:F25)</f>
         <v/>
       </c>
-      <c r="G26" s="15">
+      <c r="G26" s="17">
         <f>SUM(G11:G25)</f>
         <v/>
       </c>
-      <c r="H26" s="15">
+      <c r="H26" s="17">
         <f>SUM(H11:H25)</f>
         <v/>
       </c>
-      <c r="I26" s="15">
+      <c r="I26" s="17">
         <f>SUM(I11:I25)</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>📤  GASTOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
+    <row r="27" ht="14" customHeight="1"/>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  GASTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>Nº Recibo</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>N° Recibo</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Proveedor</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>Base €</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>IVA €</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>Total €</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>Categoría</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>IVA</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>Categoria</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>Deducible</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="9" t="n"/>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="9" t="n"/>
-      <c r="G30" s="11">
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="13">
         <f>IF(E30="","",E30+F30)</f>
         <v/>
       </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>Cuota autónomo</t>
-        </is>
-      </c>
-      <c r="I30" s="18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="n"/>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="10" t="n"/>
-      <c r="D31" s="10" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="11">
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>Cuota autonomo</t>
+        </is>
+      </c>
+      <c r="I30" s="19" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="13">
         <f>IF(E31="","",E31+F31)</f>
         <v/>
       </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>Gestoría</t>
-        </is>
-      </c>
-      <c r="I31" s="18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="n"/>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
-      <c r="G32" s="11">
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>Gestoria</t>
+        </is>
+      </c>
+      <c r="I31" s="19" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="13">
         <f>IF(E32="","",E32+F32)</f>
         <v/>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H32" s="11" t="inlineStr">
         <is>
           <t>Software</t>
         </is>
       </c>
-      <c r="I32" s="18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="n"/>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="11">
+      <c r="I32" s="19" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="13">
         <f>IF(E33="","",E33+F33)</f>
         <v/>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H33" s="11" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="I33" s="18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="n"/>
-      <c r="B34" s="9" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="9" t="n"/>
-      <c r="G34" s="11">
+      <c r="I33" s="19" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="13">
         <f>IF(E34="","",E34+F34)</f>
         <v/>
       </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>Formación</t>
-        </is>
-      </c>
-      <c r="I34" s="18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="n"/>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="9" t="n"/>
-      <c r="G35" s="11">
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>Formacion</t>
+        </is>
+      </c>
+      <c r="I34" s="19" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="13">
         <f>IF(E35="","",E35+F35)</f>
         <v/>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H35" s="11" t="inlineStr">
         <is>
           <t>Marketing</t>
         </is>
       </c>
-      <c r="I35" s="18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="9" t="n"/>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="9" t="n"/>
-      <c r="G36" s="11">
+      <c r="I35" s="19" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="13">
         <f>IF(E36="","",E36+F36)</f>
         <v/>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="H36" s="11" t="inlineStr">
         <is>
           <t>Viajes</t>
         </is>
       </c>
-      <c r="I36" s="18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="n"/>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="11">
+      <c r="I36" s="19" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="10" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="13">
         <f>IF(E37="","",E37+F37)</f>
         <v/>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>Dietas</t>
         </is>
       </c>
-      <c r="I37" s="18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="n"/>
-      <c r="B38" s="9" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="10" t="n"/>
-      <c r="E38" s="9" t="n"/>
-      <c r="F38" s="9" t="n"/>
-      <c r="G38" s="11">
+      <c r="I37" s="19" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="10" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="12" t="n"/>
+      <c r="G38" s="13">
         <f>IF(E38="","",E38+F38)</f>
         <v/>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="H38" s="11" t="inlineStr">
         <is>
           <t>Suministros</t>
         </is>
       </c>
-      <c r="I38" s="18" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="n"/>
-      <c r="B39" s="9" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="9" t="n"/>
-      <c r="F39" s="9" t="n"/>
-      <c r="G39" s="11">
+      <c r="I38" s="19" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="10" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="12" t="n"/>
+      <c r="G39" s="13">
         <f>IF(E39="","",E39+F39)</f>
         <v/>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="H39" s="11" t="inlineStr">
         <is>
           <t>Otros</t>
         </is>
       </c>
-      <c r="I39" s="19" t="inlineStr">
+      <c r="I39" s="20" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="9" t="n"/>
-      <c r="B40" s="9" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="9" t="n"/>
-      <c r="F40" s="9" t="n"/>
-      <c r="G40" s="11">
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="10" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="12" t="n"/>
+      <c r="G40" s="13">
         <f>IF(E40="","",E40+F40)</f>
         <v/>
       </c>
-      <c r="H40" s="10" t="inlineStr"/>
-      <c r="I40" s="19" t="inlineStr">
+      <c r="H40" s="11" t="inlineStr"/>
+      <c r="I40" s="20" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="9" t="n"/>
-      <c r="B41" s="9" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10" t="n"/>
-      <c r="E41" s="9" t="n"/>
-      <c r="F41" s="9" t="n"/>
-      <c r="G41" s="11">
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="10" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="12" t="n"/>
+      <c r="G41" s="13">
         <f>IF(E41="","",E41+F41)</f>
         <v/>
       </c>
-      <c r="H41" s="10" t="inlineStr"/>
-      <c r="I41" s="19" t="inlineStr">
+      <c r="H41" s="11" t="inlineStr"/>
+      <c r="I41" s="20" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="9" t="n"/>
-      <c r="B42" s="9" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="10" t="n"/>
-      <c r="E42" s="9" t="n"/>
-      <c r="F42" s="9" t="n"/>
-      <c r="G42" s="11">
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="10" t="n"/>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="12" t="n"/>
+      <c r="G42" s="13">
         <f>IF(E42="","",E42+F42)</f>
         <v/>
       </c>
-      <c r="H42" s="10" t="inlineStr"/>
-      <c r="I42" s="19" t="inlineStr">
+      <c r="H42" s="11" t="inlineStr"/>
+      <c r="I42" s="20" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="9" t="n"/>
-      <c r="B43" s="9" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
-      <c r="E43" s="9" t="n"/>
-      <c r="F43" s="9" t="n"/>
-      <c r="G43" s="11">
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="10" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="12" t="n"/>
+      <c r="F43" s="12" t="n"/>
+      <c r="G43" s="13">
         <f>IF(E43="","",E43+F43)</f>
         <v/>
       </c>
-      <c r="H43" s="10" t="inlineStr"/>
-      <c r="I43" s="19" t="inlineStr">
+      <c r="H43" s="11" t="inlineStr"/>
+      <c r="I43" s="20" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="9" t="n"/>
-      <c r="B44" s="9" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-      <c r="E44" s="9" t="n"/>
-      <c r="F44" s="9" t="n"/>
-      <c r="G44" s="11">
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="10" t="n"/>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="12" t="n"/>
+      <c r="G44" s="13">
         <f>IF(E44="","",E44+F44)</f>
         <v/>
       </c>
-      <c r="H44" s="10" t="inlineStr"/>
-      <c r="I44" s="19" t="inlineStr">
+      <c r="H44" s="11" t="inlineStr"/>
+      <c r="I44" s="20" t="inlineStr">
         <is>
           <t>Parcial</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>TOTAL GASTOS</t>
-        </is>
-      </c>
-      <c r="E45" s="21">
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  TOTAL GASTOS</t>
+        </is>
+      </c>
+      <c r="E45" s="22">
         <f>SUM(E30:E44)</f>
         <v/>
       </c>
-      <c r="F45" s="21">
+      <c r="F45" s="22">
         <f>SUM(F30:F44)</f>
         <v/>
       </c>
-      <c r="G45" s="21">
+      <c r="G45" s="22">
         <f>SUM(G30:G44)</f>
         <v/>
       </c>
     </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="22" t="inlineStr">
-        <is>
-          <t>📊  RESUMEN DEL MES</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="23" t="inlineStr">
+    <row r="46" ht="14" customHeight="1"/>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  RESUMEN DEL MES</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="24" t="inlineStr">
         <is>
           <t>Total ingresos (base):</t>
         </is>
       </c>
-      <c r="E48" s="24">
+      <c r="E48" s="25">
         <f>E26</f>
         <v/>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="25" t="inlineStr">
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="26" t="inlineStr">
         <is>
           <t>Total IVA cobrado:</t>
         </is>
       </c>
-      <c r="E49" s="26">
+      <c r="E49" s="27">
         <f>F26</f>
         <v/>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="23" t="inlineStr">
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="24" t="inlineStr">
         <is>
           <t>Total cobrado neto:</t>
         </is>
       </c>
-      <c r="E50" s="24">
+      <c r="E50" s="25">
         <f>I26</f>
         <v/>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="25" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="23" t="inlineStr">
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="26" t="inlineStr"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="28" t="inlineStr">
         <is>
           <t>Total gastos (base):</t>
         </is>
       </c>
-      <c r="E52" s="27">
+      <c r="E52" s="29">
         <f>E45</f>
         <v/>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="25" t="inlineStr">
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="26" t="inlineStr">
         <is>
           <t>Total IVA pagado:</t>
         </is>
       </c>
-      <c r="E53" s="26">
+      <c r="E53" s="27">
         <f>F45</f>
         <v/>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="23" t="inlineStr">
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="28" t="inlineStr">
         <is>
           <t>Total gastado:</t>
         </is>
       </c>
-      <c r="E54" s="27">
+      <c r="E54" s="29">
         <f>G45</f>
         <v/>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="25" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="23" t="inlineStr">
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="26" t="inlineStr"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="30" t="inlineStr">
         <is>
           <t>RESULTADO NETO:</t>
         </is>
       </c>
-      <c r="E56" s="28">
+      <c r="E56" s="31">
         <f>E26-E45</f>
         <v/>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="23" t="inlineStr">
-        <is>
-          <t>IVA A DECLARAR (303):</t>
-        </is>
-      </c>
-      <c r="E57" s="29">
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="32" t="inlineStr">
+        <is>
+          <t>IVA A DECLARAR (modelo 303):</t>
+        </is>
+      </c>
+      <c r="E57" s="33">
         <f>F26-F45</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A56:D56"/>
+  <mergeCells count="21">
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A52:D52"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A47:I47"/>
-    <mergeCell ref="A28:I28"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="A53:D53"/>
     <mergeCell ref="A48:D48"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A51:D51"/>
     <mergeCell ref="A49:D49"/>
     <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A28:I28"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A57:D57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1572,408 +1655,409 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>RESUMEN ANUAL DE INGRESOS Y GASTOS</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="30" t="inlineStr">
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Mes</t>
         </is>
       </c>
-      <c r="B3" s="30" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Ingresos Base</t>
         </is>
       </c>
-      <c r="C3" s="30" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>IVA Cobrado</t>
         </is>
       </c>
-      <c r="D3" s="30" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>IRPF Ret.</t>
         </is>
       </c>
-      <c r="E3" s="30" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Cobrado Neto</t>
         </is>
       </c>
-      <c r="F3" s="30" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>Gastos Base</t>
         </is>
       </c>
-      <c r="G3" s="30" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>IVA Pagado</t>
         </is>
       </c>
-      <c r="H3" s="30" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Gasto Total</t>
         </is>
       </c>
-      <c r="I3" s="30" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Resultado</t>
         </is>
       </c>
-      <c r="J3" s="30" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>IVA 303</t>
         </is>
       </c>
-      <c r="K3" s="30" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="31" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>Enero</t>
         </is>
       </c>
-      <c r="B4" s="32" t="n"/>
-      <c r="C4" s="32" t="n"/>
-      <c r="D4" s="32" t="n"/>
-      <c r="E4" s="32" t="n"/>
-      <c r="F4" s="32" t="n"/>
-      <c r="G4" s="32" t="n"/>
-      <c r="H4" s="32" t="n"/>
-      <c r="I4" s="33">
+      <c r="B4" s="36" t="n"/>
+      <c r="C4" s="36" t="n"/>
+      <c r="D4" s="36" t="n"/>
+      <c r="E4" s="36" t="n"/>
+      <c r="F4" s="36" t="n"/>
+      <c r="G4" s="36" t="n"/>
+      <c r="H4" s="36" t="n"/>
+      <c r="I4" s="37">
         <f>IF(B4=0,"",B4-F4)</f>
         <v/>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="38">
         <f>IF(C4=0,"",C4-G4)</f>
         <v/>
       </c>
-      <c r="K4" s="35" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="K4" s="39" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>Febrero</t>
         </is>
       </c>
-      <c r="B5" s="32" t="n"/>
-      <c r="C5" s="32" t="n"/>
-      <c r="D5" s="32" t="n"/>
-      <c r="E5" s="32" t="n"/>
-      <c r="F5" s="32" t="n"/>
-      <c r="G5" s="32" t="n"/>
-      <c r="H5" s="32" t="n"/>
-      <c r="I5" s="33">
+      <c r="B5" s="36" t="n"/>
+      <c r="C5" s="36" t="n"/>
+      <c r="D5" s="36" t="n"/>
+      <c r="E5" s="36" t="n"/>
+      <c r="F5" s="36" t="n"/>
+      <c r="G5" s="36" t="n"/>
+      <c r="H5" s="36" t="n"/>
+      <c r="I5" s="37">
         <f>IF(B5=0,"",B5-F5)</f>
         <v/>
       </c>
-      <c r="J5" s="34">
+      <c r="J5" s="38">
         <f>IF(C5=0,"",C5-G5)</f>
         <v/>
       </c>
-      <c r="K5" s="35" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="31" t="inlineStr">
+      <c r="K5" s="39" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>Marzo</t>
         </is>
       </c>
-      <c r="B6" s="32" t="n"/>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="32" t="n"/>
-      <c r="E6" s="32" t="n"/>
-      <c r="F6" s="32" t="n"/>
-      <c r="G6" s="32" t="n"/>
-      <c r="H6" s="32" t="n"/>
-      <c r="I6" s="33">
+      <c r="B6" s="36" t="n"/>
+      <c r="C6" s="36" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
+      <c r="F6" s="36" t="n"/>
+      <c r="G6" s="36" t="n"/>
+      <c r="H6" s="36" t="n"/>
+      <c r="I6" s="37">
         <f>IF(B6=0,"",B6-F6)</f>
         <v/>
       </c>
-      <c r="J6" s="34">
+      <c r="J6" s="38">
         <f>IF(C6=0,"",C6-G6)</f>
         <v/>
       </c>
-      <c r="K6" s="35" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="K6" s="39" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>Abril</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n"/>
-      <c r="C7" s="32" t="n"/>
-      <c r="D7" s="32" t="n"/>
-      <c r="E7" s="32" t="n"/>
-      <c r="F7" s="32" t="n"/>
-      <c r="G7" s="32" t="n"/>
-      <c r="H7" s="32" t="n"/>
-      <c r="I7" s="33">
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="36" t="n"/>
+      <c r="I7" s="37">
         <f>IF(B7=0,"",B7-F7)</f>
         <v/>
       </c>
-      <c r="J7" s="34">
+      <c r="J7" s="38">
         <f>IF(C7=0,"",C7-G7)</f>
         <v/>
       </c>
-      <c r="K7" s="35" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="K7" s="39" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>Mayo</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n"/>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="32" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="32" t="n"/>
-      <c r="G8" s="32" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="33">
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="36" t="n"/>
+      <c r="I8" s="37">
         <f>IF(B8=0,"",B8-F8)</f>
         <v/>
       </c>
-      <c r="J8" s="34">
+      <c r="J8" s="38">
         <f>IF(C8=0,"",C8-G8)</f>
         <v/>
       </c>
-      <c r="K8" s="35" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="31" t="inlineStr">
+      <c r="K8" s="39" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>Junio</t>
         </is>
       </c>
-      <c r="B9" s="32" t="n"/>
-      <c r="C9" s="32" t="n"/>
-      <c r="D9" s="32" t="n"/>
-      <c r="E9" s="32" t="n"/>
-      <c r="F9" s="32" t="n"/>
-      <c r="G9" s="32" t="n"/>
-      <c r="H9" s="32" t="n"/>
-      <c r="I9" s="33">
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
+      <c r="I9" s="37">
         <f>IF(B9=0,"",B9-F9)</f>
         <v/>
       </c>
-      <c r="J9" s="34">
+      <c r="J9" s="38">
         <f>IF(C9=0,"",C9-G9)</f>
         <v/>
       </c>
-      <c r="K9" s="35" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="K9" s="39" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>Julio</t>
         </is>
       </c>
-      <c r="B10" s="32" t="n"/>
-      <c r="C10" s="32" t="n"/>
-      <c r="D10" s="32" t="n"/>
-      <c r="E10" s="32" t="n"/>
-      <c r="F10" s="32" t="n"/>
-      <c r="G10" s="32" t="n"/>
-      <c r="H10" s="32" t="n"/>
-      <c r="I10" s="33">
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
+      <c r="I10" s="37">
         <f>IF(B10=0,"",B10-F10)</f>
         <v/>
       </c>
-      <c r="J10" s="34">
+      <c r="J10" s="38">
         <f>IF(C10=0,"",C10-G10)</f>
         <v/>
       </c>
-      <c r="K10" s="35" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="K10" s="39" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>Agosto</t>
         </is>
       </c>
-      <c r="B11" s="32" t="n"/>
-      <c r="C11" s="32" t="n"/>
-      <c r="D11" s="32" t="n"/>
-      <c r="E11" s="32" t="n"/>
-      <c r="F11" s="32" t="n"/>
-      <c r="G11" s="32" t="n"/>
-      <c r="H11" s="32" t="n"/>
-      <c r="I11" s="33">
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="37">
         <f>IF(B11=0,"",B11-F11)</f>
         <v/>
       </c>
-      <c r="J11" s="34">
+      <c r="J11" s="38">
         <f>IF(C11=0,"",C11-G11)</f>
         <v/>
       </c>
-      <c r="K11" s="35" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="K11" s="39" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>Septiembre</t>
         </is>
       </c>
-      <c r="B12" s="32" t="n"/>
-      <c r="C12" s="32" t="n"/>
-      <c r="D12" s="32" t="n"/>
-      <c r="E12" s="32" t="n"/>
-      <c r="F12" s="32" t="n"/>
-      <c r="G12" s="32" t="n"/>
-      <c r="H12" s="32" t="n"/>
-      <c r="I12" s="33">
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n"/>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="37">
         <f>IF(B12=0,"",B12-F12)</f>
         <v/>
       </c>
-      <c r="J12" s="34">
+      <c r="J12" s="38">
         <f>IF(C12=0,"",C12-G12)</f>
         <v/>
       </c>
-      <c r="K12" s="35" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="K12" s="39" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>Octubre</t>
         </is>
       </c>
-      <c r="B13" s="32" t="n"/>
-      <c r="C13" s="32" t="n"/>
-      <c r="D13" s="32" t="n"/>
-      <c r="E13" s="32" t="n"/>
-      <c r="F13" s="32" t="n"/>
-      <c r="G13" s="32" t="n"/>
-      <c r="H13" s="32" t="n"/>
-      <c r="I13" s="33">
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+      <c r="I13" s="37">
         <f>IF(B13=0,"",B13-F13)</f>
         <v/>
       </c>
-      <c r="J13" s="34">
+      <c r="J13" s="38">
         <f>IF(C13=0,"",C13-G13)</f>
         <v/>
       </c>
-      <c r="K13" s="35" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="31" t="inlineStr">
+      <c r="K13" s="39" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>Noviembre</t>
         </is>
       </c>
-      <c r="B14" s="32" t="n"/>
-      <c r="C14" s="32" t="n"/>
-      <c r="D14" s="32" t="n"/>
-      <c r="E14" s="32" t="n"/>
-      <c r="F14" s="32" t="n"/>
-      <c r="G14" s="32" t="n"/>
-      <c r="H14" s="32" t="n"/>
-      <c r="I14" s="33">
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="36" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="36" t="n"/>
+      <c r="I14" s="37">
         <f>IF(B14=0,"",B14-F14)</f>
         <v/>
       </c>
-      <c r="J14" s="34">
+      <c r="J14" s="38">
         <f>IF(C14=0,"",C14-G14)</f>
         <v/>
       </c>
-      <c r="K14" s="35" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="K14" s="39" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="B15" s="32" t="n"/>
-      <c r="C15" s="32" t="n"/>
-      <c r="D15" s="32" t="n"/>
-      <c r="E15" s="32" t="n"/>
-      <c r="F15" s="32" t="n"/>
-      <c r="G15" s="32" t="n"/>
-      <c r="H15" s="32" t="n"/>
-      <c r="I15" s="33">
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="37">
         <f>IF(B15=0,"",B15-F15)</f>
         <v/>
       </c>
-      <c r="J15" s="34">
+      <c r="J15" s="38">
         <f>IF(C15=0,"",C15-G15)</f>
         <v/>
       </c>
-      <c r="K15" s="35" t="n"/>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="36" t="inlineStr">
+      <c r="K15" s="39" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="40" t="inlineStr">
         <is>
           <t>TOTAL AÑO</t>
         </is>
       </c>
-      <c r="B16" s="37">
+      <c r="B16" s="41">
         <f>SUM(B4:B15)</f>
         <v/>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="41">
         <f>SUM(C4:C15)</f>
         <v/>
       </c>
-      <c r="D16" s="37">
+      <c r="D16" s="41">
         <f>SUM(D4:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="37">
+      <c r="E16" s="41">
         <f>SUM(E4:E15)</f>
         <v/>
       </c>
-      <c r="F16" s="37">
+      <c r="F16" s="41">
         <f>SUM(F4:F15)</f>
         <v/>
       </c>
-      <c r="G16" s="37">
+      <c r="G16" s="41">
         <f>SUM(G4:G15)</f>
         <v/>
       </c>
-      <c r="H16" s="37">
+      <c r="H16" s="41">
         <f>SUM(H4:H15)</f>
         <v/>
       </c>
-      <c r="I16" s="37">
+      <c r="I16" s="41">
         <f>SUM(I4:I15)</f>
         <v/>
       </c>
-      <c r="J16" s="37">
+      <c r="J16" s="41">
         <f>SUM(J4:J15)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A16"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1985,156 +2069,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="38" t="inlineStr">
-        <is>
-          <t>CÓMO USAR ESTA PLANTILLA</t>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>INSTRUCCIONES — Registro de Ingresos y Gastos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr"/>
-    </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>📥 PESTAÑA REGISTRO MENSUAL</t>
+      <c r="A2" s="43" t="inlineStr"/>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="44" t="inlineStr">
+        <is>
+          <t>PESTANA REGISTRO MENSUAL</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="39" t="inlineStr">
-        <is>
-          <t>1. Cambia el Año, Mes y tu nombre en la sección CONFIGURACIÓN (celdas naranjas).</t>
+      <c r="A4" s="45" t="inlineStr">
+        <is>
+          <t>1. Cambia el Año, Mes y tu nombre en la seccion CONFIGURACION</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="inlineStr">
-        <is>
-          <t>2. En la sección INGRESOS, introduce una fila por cada factura emitida.</t>
+      <c r="A5" s="45" t="inlineStr">
+        <is>
+          <t>2. En INGRESOS: una fila por factura emitida. La columna Total se calcula sola.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
-        <is>
-          <t>3. La columna 'Total €' (Ingresos) se calcula automáticamente: Base + IVA.</t>
+      <c r="A6" s="45" t="inlineStr">
+        <is>
+          <t>3. En GASTOS: todos los gastos del negocio organizados por categoria.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
-        <is>
-          <t>4. La columna 'Cobrado €' descuenta la retención de IRPF automáticamente.</t>
+      <c r="A7" s="45" t="inlineStr">
+        <is>
+          <t>4. El RESUMEN al final muestra resultado neto y el IVA a declarar (modelo 303).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="inlineStr">
-        <is>
-          <t>5. En la sección GASTOS, introduce todos los gastos del negocio con factura.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="39" t="inlineStr">
-        <is>
-          <t>6. El RESUMEN al final te muestra el resultado neto y el IVA a declarar.</t>
+      <c r="A8" s="43" t="inlineStr"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="46" t="inlineStr">
+        <is>
+          <t>PESTANA RESUMEN ANUAL</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>📊 PESTAÑA RESUMEN ANUAL</t>
+      <c r="A10" s="45" t="inlineStr">
+        <is>
+          <t>Introduce los totales de cada mes para ver el año completo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="45" t="inlineStr">
+        <is>
+          <t>La fila TOTAL AÑO suma los 12 meses automaticamente.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
-        <is>
-          <t>• Introduce manualmente los totales de cada mes para ver el año completo.</t>
-        </is>
-      </c>
+      <c r="A12" s="43" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="inlineStr">
-        <is>
-          <t>• La fila 'TOTAL AÑO' suma automáticamente los 12 meses.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="39" t="inlineStr">
-        <is>
-          <t>• Úsala para preparar tus declaraciones trimestrales (IVA y IRPF).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="25" t="inlineStr"/>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>⚠️ NOTAS IMPORTANTES</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="39" t="inlineStr">
-        <is>
-          <t>• Las celdas con fondo naranja son editables. Las blancas tienen fórmulas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="39" t="inlineStr">
-        <is>
-          <t>• Esta plantilla NO sustituye a la contabilidad oficial. Úsala como registro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="39" t="inlineStr">
-        <is>
-          <t>• Para España: IVA general 21%, reducido 10%, superreducido 4%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="39" t="inlineStr">
-        <is>
-          <t>• Retención IRPF: 15% profesionales con +2 años, 7% los primeros 2 años.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="25" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="40" t="inlineStr">
-        <is>
-          <t>🌐 Más herramientas gratuitas en autonomolab.com</t>
+      <c r="A13" s="47" t="inlineStr">
+        <is>
+          <t>Mas herramientas gratuitas en: autonomolab.com</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
